--- a/Prog poussin/Popo/output/Plan_Livraisons_BELGO_Ponte.xlsx
+++ b/Prog poussin/Popo/output/Plan_Livraisons_BELGO_Ponte.xlsx
@@ -557,3412 +557,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L107"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="70" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Plan de production : Jeu 04/06 = 30,000 | Ven 05/06 = 38,000 | Mer 10/06 = 15,000 | Jeu 11/06 = 38,000 | Lun 15/06 = 30,000 | Ven 19/06 = 38,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Date éclosion</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Capacité production</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Tiers</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Réf. Tiers</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Qté à livrer</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Qté totale commande</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Région</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Agence</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Date prévue livraison</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Statut échéance</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Jeu 04/06/2026 — Production: 30,000 | Region: Centre + Littoral + Ouest | Place libre: 350 [Littoral minime: 5,800 (ÉCHUE: 5,500)]</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Bobga Stanly Gima</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45438</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Mogum Fossi Laurence Lor</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-51968</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Star Car Company S.a</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-54855</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53611</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Emale Tache Bertrand Patrick (42E32)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53565</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>TAKAMTSING PROSPER</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55438</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>4250</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>4250</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55641</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>2850</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>2850</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Likeng Jean Paul (Likeng Jean Paul)</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53042</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Che Clarisse Mbouda</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-46181</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>850</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>850</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>BELGO MBOUDA</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>KUATE KENGNE MATHIAS</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-47945</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>4600</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>4600</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Simnoue Benjamin</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52468</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>NGAPINSI  ROMIAL</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45280</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>TEDONGMO ZOYIM AGOSTINI</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-50425</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>BOUKAR ISAIE</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52017</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>3100</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Jeu 04/06</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="7" t="n">
-        <v>29650</v>
-      </c>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Ven 05/06/2026 — Production: 38,000 | Region: Centre + Ouest | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>GIC LOIC</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-51319</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>18200</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>18200</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NKOABANG</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>NDAMSA DICKSON THOMAS</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-48600</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>BELGO MBOUDA</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>GATCHUESSI</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53410</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>DASSI BERTRAND(DG)</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53793</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>DJOUWE GUTCHOU JULIETTE STEPHANIE</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-54019</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>NKOUAMOU JEAN JULES</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-54145</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TALLA TAGNE SERGE RICHARD</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-54827</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>3300</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Lukong Epse Ebango</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-46831</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Ven 05/06</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="7" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Mer 10/06/2026 — Production: 15,000 | Region: Ouest | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>FOTSING KOUDJOU ERIC MARTIAL</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45243</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>NGAPINSI  ROMIAL</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45280</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>4850</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Wayap Guy Merlin</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45568</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>3650</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Suite -&gt; 11/06 (1j) | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Mer 10/06</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Jeu 11/06/2026 — Production: 38,000 | Region: Ouest | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Wayap Guy Merlin</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-45568</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1550</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>NGAPINSI  ROMIAL</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>SO2601-42521</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>2700</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>2700</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>KUATE NOKAM GUY SALOMON</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-46922</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Fokou Nono Herve Raoul</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55346</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>TAGNE ROGER</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-47538</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>2300</v>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Tchinda Kuekou Victor</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-47750</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>27/06/2026</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>PEKA TAGNE IGNACE</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-47700</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>9250</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>9250</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>KOAGNE FOTSO MICHEL</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-47845</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>PEKA TAGNE IGNACE</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55242</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>11700</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>12750</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Jeu 11/06</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="7" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-      <c r="L50" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Lun 15/06/2026 — Production: 30,000 | Region: Centre | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55799</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>16650</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>16650</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L53" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>KENNE TAKALA BRICE</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55818</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>3300</v>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L54" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>TALOM TELESPHORE</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-46115</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NKOABANG</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L55" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>FOMEKONG</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>SO2602-46172</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L56" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>TAKAMTSING PROSPER</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-49472</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Tenangfie Orthance Atsomh</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-48378</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>2750</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L58" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Lun 15/06</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
-      <c r="L59" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Ven 19/06/2026 — Production: 38,000 | Region: Littoral + Nord | Place libre: 0 [Littoral minime: 9,050 (ÉCHUE: 0)]</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>WANDJI ELISABETH</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-56192</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="L62" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Koumetio Keubou David Herve</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-55726</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NKONGSAMBA</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>ABDOUL AZIZ</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52437</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L64" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Sandeep Tirkey</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>SO2605-56126</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>&lt;=1000 | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>COGESDI SARL</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-49144</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>10250</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>10250</v>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>MIBE GUY MARCIAL</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-50464</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>BELGO VILLAGE</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53508</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L68" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53824</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Tchinda Zephirin (Tchinda Zephirin)</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-50402</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L70" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>NOUPING</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52451</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>TEFACK DASSI HERVE</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>SO2603-50650</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L72" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>COGESDI SARL</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-51013</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Chefor Shadrack Nchang</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53200</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BUEA</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L74" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>HASSAN HAROUNA</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52671</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>23/08/2026</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Menquele Rodrigue</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-53285</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L76" s="6" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>BOUKAR ISAIE</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>SO2604-52017</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>3100</v>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>BELGO-BERI</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L77" s="6" t="inlineStr">
-        <is>
-          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total Ven 19/06</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="7" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
-      <c r="L78" s="8" t="n"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL GENERAL LIVRE</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="n"/>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-      <c r="F80" s="12" t="n">
-        <v>188650</v>
-      </c>
-      <c r="G80" s="13" t="n"/>
-      <c r="H80" s="13" t="n"/>
-      <c r="I80" s="13" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="13" t="n"/>
-      <c r="L80" s="13" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL QTE MANQUANTE (capacité disponible)</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>Legende :</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>ECHUE</t>
-        </is>
-      </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>Commande dont la date prevue de livraison est depassee</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>ECHUE RECLASSEE</t>
-        </is>
-      </c>
-      <c r="D85" s="18" t="inlineStr">
-        <is>
-          <t>Commande echue + reclassee (date_modif &lt; date_prevue - 5j)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>IMMINENTE</t>
-        </is>
-      </c>
-      <c r="D86" s="18" t="inlineStr">
-        <is>
-          <t>Livraison prevue &lt;=10j — integree uniquement en force majeure</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>NON ECHUE</t>
-        </is>
-      </c>
-      <c r="D87" s="18" t="inlineStr">
-        <is>
-          <t>Livraison pas encore due — non integrable</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>Livraison partielle — premier split &gt;= 50% de la qte totale, pas de 2e split</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>FORCE MAJEURE</t>
-        </is>
-      </c>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>Commande imminente integree pour remplir la capacite</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>EST+NORD</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>Est et Nord toujours programmes le meme jour (preference jeu/ven)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>MOUVEMENT SYSTEME</t>
-        </is>
-      </c>
-      <c r="D91" s="18" t="inlineStr">
-        <is>
-          <t>Mouvement automatique Proctor Ai "En cours" (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>QTE MANQUANTE</t>
-        </is>
-      </c>
-      <c r="D92" s="18" t="inlineStr">
-        <is>
-          <t>Capacite non utilisee — disponible pour insertion ulterieure (pas de split force)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>Contraintes appliquees :</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>1. FIFO par date de livraison prevue (echues en priorite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>2. Commandes &lt;=1000 echues traitees en premier (sauf Est/Nord -&gt; meme jour)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>3. Est et Nord TOUJOURS programmes le meme jour (preference jeu/ven pour eclosion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="19" t="inlineStr">
-        <is>
-          <t>4. Une region principale par jour (completee si capacite restante)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>5. Client TEDONGMO YEMDJI FRANCK exclu</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>6. Commandes en statut Brouillon exclues</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>7. Proctor Ai 'En cours' = mouvement systeme / Proctor Ai 'Livree' = livraison reelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="19" t="inlineStr">
-        <is>
-          <t>8. Commandes non echues integrees uniquement en force majeure</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>9. Livraison en 2 fois possible : 2-3j meme semaine, 4-5j cross-semaine</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>10. Quantites deja livrees (reelles) deduites via fichier A traiter</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="19" t="inlineStr">
-        <is>
-          <t>11. Cross-reference expeditions pour filtrage Proctor Ai + Status Commande</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="19" t="inlineStr">
-        <is>
-          <t>12. Date de reference: 09/05/2026 (dates anterieures exclues)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="19" t="inlineStr">
-        <is>
-          <t>13. Pas de split non pertinent: premier split &gt;= 50% de la qte totale, pas de 2e split (totalite du reste) — capacite restante = qte manquante informative</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B2:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7025,13 +3619,2952 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:L98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Plan de production : Jeu 04/06 = 26,400 | Ven 05/06 = 33,900 | Mer 10/06 = 12,150 | Jeu 11/06 = 33,550 | Lun 15/06 = 25,750 | Ven 19/06 = 34,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Date éclosion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Capacité production</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tiers</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Réf. Tiers</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Qté à livrer</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Qté totale commande</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Région</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Agence</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Date prévue livraison</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Statut échéance</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Jeu 04/06/2026 — Production: 26,400 | Region: Centre + Littoral + Ouest | Place libre: 0 [Littoral minime: 5,500 (ÉCHUE: 5,500)]</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Bobga Stanly Gima</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-45438</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Mogum Fossi Laurence Lor</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-51968</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Star Car Company S.a</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-54855</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-53611</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Emale Tache Bertrand Patrick (42E32)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-53565</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55438</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55641</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Likeng Jean Paul (Likeng Jean Paul)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-53042</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Che Clarisse Mbouda</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46181</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>850</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>850</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>KUATE KENGNE MATHIAS</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-47945</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Suite -&gt; 05/06 (1j) | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Jeu 04/06</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="7" t="n">
+        <v>26400</v>
+      </c>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Ven 05/06/2026 — Production: 33,900 | Region: Littoral + Ouest | Place libre: 100 [Littoral minime: 500 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>KUATE KENGNE MATHIAS</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-47945</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Simnoue Benjamin</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-52468</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>NDAMSA DICKSON THOMAS</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-48600</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>GATCHUESSI</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-53410</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>DASSI BERTRAND(DG)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-53793</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>DJOUWE GUTCHOU JULIETTE STEPHANIE</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-54019</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>NKOUAMOU JEAN JULES</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-54145</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TALLA TAGNE SERGE RICHARD</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-54827</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>FOTSING KOUDJOU ERIC MARTIAL</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-45243</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-50425</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>NGAPINSI  ROMIAL</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-45280</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>MIBE GUY MARCIAL</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-50464</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>BELGO VILLAGE</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Ven 05/06</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="7" t="n">
+        <v>33800</v>
+      </c>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Qté manquante pour compléter la production</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Capacité disponible pour insertion ultérieure</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Mer 10/06/2026 — Production: 12,150 | Region: Ouest | Place libre: 0</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Wayap Guy Merlin</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-45568</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>NGAPINSI  ROMIAL</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>SO2601-42521</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>PEKA TAGNE IGNACE</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55242</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>12750</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-49249</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>3700</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Mer 10/06</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="7" t="n">
+        <v>12150</v>
+      </c>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Jeu 11/06/2026 — Production: 33,550 | Region: Centre + Littoral | Place libre: 0 [Littoral minime: 1,500 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>GIC LOIC</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>SO2604-51319</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>18200</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NKOABANG</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>FOMEKONG</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46172</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Suite -&gt; 15/06 (4j) | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-49472</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Tenangfie Orthance Atsomh</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-48378</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>FIDELIA EPSE CHETEU</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46599</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NKOABANG</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Ndougom Francis</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-47491</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>2350</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NKOABANG</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Lukong Epse Ebango</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46831</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>MIBE GUY MARCIAL</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>SO2603-50464</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>BELGO VILLAGE</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Jeu 11/06</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="7" t="n">
+        <v>33550</v>
+      </c>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Lun 15/06/2026 — Production: 25,750 | Region: Centre | Place libre: 0</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>25750</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55799</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>16650</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>16650</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>25750</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>KENNE TAKALA BRICE</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55818</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>25750</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>TALOM TELESPHORE</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46115</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NKOABANG</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>25750</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>FOMEKONG</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46172</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Lun 15/06</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="7" t="n">
+        <v>25750</v>
+      </c>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Ven 19/06/2026 — Production: 34,100 | Region: Littoral + Ouest | Place libre: 0 [Littoral minime: 1,700 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>WANDJI ELISABETH</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-56192</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>KUATE NOKAM GUY SALOMON</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-46922</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Koumetio Keubou David Herve</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55726</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NKONGSAMBA</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Fokou Nono Herve Raoul</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55346</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>TAGNE ROGER</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-47538</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Tchinda Kuekou Victor</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-47750</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>PEKA TAGNE IGNACE</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-47700</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>9250</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>9250</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>KOAGNE FOTSO MICHEL</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>SO2602-47845</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>PEKA TAGNE IGNACE</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-55242</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>10350</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>12750</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total Ven 19/06</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="7" t="n">
+        <v>34100</v>
+      </c>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL LIVRE</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+      <c r="F71" s="12" t="n">
+        <v>165750</v>
+      </c>
+      <c r="G71" s="13" t="n"/>
+      <c r="H71" s="13" t="n"/>
+      <c r="I71" s="13" t="n"/>
+      <c r="J71" s="13" t="n"/>
+      <c r="K71" s="13" t="n"/>
+      <c r="L71" s="13" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL QTE MANQUANTE (capacité disponible)</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Legende :</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>ECHUE</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Commande dont la date prevue de livraison est depassee</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>ECHUE RECLASSEE</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>Commande echue + reclassee (date_modif &lt; date_prevue - 5j)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Livraison prevue &lt;=10j — integree uniquement en force majeure</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>NON ECHUE</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Livraison pas encore due — non integrable</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>SPLIT</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Livraison partielle — premier split &gt;= 50% de la qte totale, pas de 2e split</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Commande imminente integree pour remplir la capacite</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>EST+NORD</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Est et Nord toujours programmes le meme jour (preference jeu/ven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>MOUVEMENT SYSTEME</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Mouvement automatique Proctor Ai "En cours" (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>QTE MANQUANTE</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>Capacite non utilisee — disponible pour insertion ulterieure (pas de split force)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Contraintes appliquees :</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>1. FIFO par date de livraison prevue (echues en priorite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>2. Commandes &lt;=1000 echues traitees en premier (sauf Est/Nord -&gt; meme jour)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>3. Est et Nord TOUJOURS programmes le meme jour (preference jeu/ven pour eclosion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>4. Une region principale par jour (completee si capacite restante)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>5. Client TEDONGMO YEMDJI FRANCK exclu</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>6. Commandes en statut Brouillon exclues</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>7. Proctor Ai 'En cours' = mouvement systeme / Proctor Ai 'Livree' = livraison reelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>8. Commandes non echues integrees uniquement en force majeure</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>9. Livraison en 2 fois possible : 2-3j meme semaine, 4-5j cross-semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>10. Quantites deja livrees (reelles) deduites via fichier A traiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>11. Cross-reference expeditions pour filtrage Proctor Ai + Status Commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>12. Date de reference: 09/05/2026 (dates anterieures exclues)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>13. Pas de split non pertinent: premier split &gt;= 50% de la qte totale, pas de 2e split (totalite du reste) — capacite restante = qte manquante informative</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I70"/>
+  <dimension ref="B2:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7097,28 +6630,28 @@
     <row r="5">
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>DOUANLA SIMPLICE</t>
+          <t>KENMEGNE EPSE KOUAM THERESE SYLVIE</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>SO2603-48403</t>
+          <t>SO2602-46588</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -7128,35 +6661,35 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>PEKA TAGNE IGNACE</t>
+          <t>SOFAB PROVENDERIE</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55242</t>
+          <t>SO2602-47755</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12750</v>
+        <v>4400</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12750</v>
+        <v>4400</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -7166,26 +6699,26 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>TSAFACK  ROBERT</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55433</t>
+          <t>SO2602-47754</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8850</v>
+        <v>5600</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>8850</v>
+        <v>5600</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -7204,35 +6737,35 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>DJEMENI KAMENI</t>
+          <t>DOUANLA SIMPLICE</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>SO2603-48511</t>
+          <t>SO2603-48403</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2850</v>
+        <v>25000</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOLBISSON</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -7242,26 +6775,26 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SOFAB PROVENDERIE</t>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49185</t>
+          <t>SO2605-55433</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3500</v>
+        <v>8850</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3500</v>
+        <v>8850</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -7280,26 +6813,26 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>GLOBAL BUSINESS</t>
+          <t>DJEMENI KAMENI</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>SO2603-48726</t>
+          <t>SO2603-48511</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>23500</v>
+        <v>7000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>23500</v>
+        <v>7000</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -7308,7 +6841,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKOLBISSON</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -7318,35 +6851,35 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>COGESDI SARL</t>
+          <t>SOFAB PROVENDERIE</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49144</t>
+          <t>SO2603-49185</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>10250</v>
+        <v>3500</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>10250</v>
+        <v>3500</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -7356,26 +6889,26 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ETS FERME NGASCHO (4E94)</t>
+          <t>GLOBAL BUSINESS</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49488</t>
+          <t>SO2603-48726</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4700</v>
+        <v>23500</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4700</v>
+        <v>23500</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -7384,7 +6917,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -7394,35 +6927,35 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>WAFIN GAELLE</t>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49436</t>
+          <t>SO2603-49249</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>10000</v>
+        <v>1850</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>10000</v>
+        <v>3700</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -7432,35 +6965,35 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>GIC FAMES</t>
+          <t>COGESDI SARL</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49511</t>
+          <t>SO2603-49144</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4200</v>
+        <v>10250</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4200</v>
+        <v>10250</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -7470,35 +7003,35 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>KAMGANG GHISLAIN</t>
+          <t>ETS FERME NGASCHO (4E94)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49742</t>
+          <t>SO2603-49488</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6500</v>
+        <v>4700</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>6500</v>
+        <v>4700</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -7508,35 +7041,35 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>VOKENG KENANG GUILIANO HERVE</t>
+          <t>WAFIN GAELLE</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>SO2603-49819</t>
+          <t>SO2603-49436</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -7546,26 +7079,26 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>LAMINE BOUBA</t>
+          <t>GIC FAMES</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50019</t>
+          <t>SO2603-49511</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5500</v>
+        <v>4200</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5500</v>
+        <v>4200</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -7574,7 +7107,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -7584,35 +7117,35 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MIBE GUY MARCIAL</t>
+          <t>KAMGANG GHISLAIN</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50464</t>
+          <t>SO2603-49742</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>BELGO VILLAGE</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -7622,35 +7155,35 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
+          <t>VOKENG KENANG GUILIANO HERVE</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53508</t>
+          <t>SO2603-49819</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -7660,35 +7193,35 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
+          <t>LAMINE BOUBA</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53824</t>
+          <t>SO2603-50019</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -7698,26 +7231,26 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tchinda Zephirin (Tchinda Zephirin)</t>
+          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50402</t>
+          <t>SO2604-53508</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4100</v>
+        <v>2000</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4100</v>
+        <v>2000</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -7736,35 +7269,35 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>KENNY PATRICK</t>
+          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50649</t>
+          <t>SO2604-53824</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -7774,35 +7307,35 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>PROVENDERIE L' ASSURANCE</t>
+          <t>Tchinda Zephirin (Tchinda Zephirin)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50691</t>
+          <t>SO2603-50402</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -7812,35 +7345,35 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>NOUPING</t>
+          <t>KENNY PATRICK</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52451</t>
+          <t>SO2603-50649</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -7857,28 +7390,28 @@
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>TEFACK DASSI HERVE</t>
+          <t>PROVENDERIE L' ASSURANCE</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>SO2603-50650</t>
+          <t>SO2603-50691</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -7888,35 +7421,35 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>COGESDI SARL</t>
+          <t>NOUPING</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51013</t>
+          <t>SO2604-52451</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -7926,35 +7459,35 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>TEFACK DASSI HERVE</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51282</t>
+          <t>SO2603-50650</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>5800</v>
+        <v>3600</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5800</v>
+        <v>3600</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -7964,19 +7497,19 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>SANDJONG ELIE</t>
+          <t>COGESDI SARL</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51281</t>
+          <t>SO2604-51013</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -7987,12 +7520,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -8002,35 +7535,35 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Chefor Shadrack Nchang</t>
+          <t>TAKAMTSING PROSPER</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53200</t>
+          <t>SO2604-51282</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1050</v>
+        <v>5800</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1050</v>
+        <v>5800</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>BELGO-BUEA</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -8047,12 +7580,12 @@
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>HASSAN HAROUNA</t>
+          <t>SANDJONG ELIE</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52671</t>
+          <t>SO2604-51281</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -8063,12 +7596,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -8078,35 +7611,35 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>KENNE TCHUENTE JILDAS ANICET</t>
+          <t>Chefor Shadrack Nchang</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51270</t>
+          <t>SO2604-53200</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>3000</v>
+        <v>1050</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>3000</v>
+        <v>1050</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-BUEA</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -8116,26 +7649,26 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Menquele Rodrigue</t>
+          <t>HASSAN HAROUNA</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53285</t>
+          <t>SO2604-52671</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -8154,26 +7687,26 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>KAMTA SIEWE EPSE TCHATCHOUA EMILIENNE</t>
+          <t>KENNE TCHUENTE JILDAS ANICET</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51800</t>
+          <t>SO2604-51270</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>5200</v>
+        <v>3000</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>5200</v>
+        <v>3000</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -8192,35 +7725,35 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PIEBJOU MICHEL</t>
+          <t>Menquele Rodrigue</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51756</t>
+          <t>SO2604-53285</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -8237,28 +7770,28 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>ABDOUL AZIZ</t>
+          <t>KAMTA SIEWE EPSE TCHATCHOUA EMILIENNE</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52437</t>
+          <t>SO2604-51800</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -8268,26 +7801,26 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>KAMDEM MERLIN</t>
+          <t>PIEBJOU MICHEL</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51411</t>
+          <t>SO2604-51756</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>23000</v>
+        <v>2100</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>23000</v>
+        <v>2100</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -8296,7 +7829,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -8306,35 +7839,35 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ETABLISSEMENT KAFAB SARL (KAMDEM FOTSO ACHILLE BERTRAND)</t>
+          <t>ABDOUL AZIZ</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53917</t>
+          <t>SO2604-52437</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -8344,35 +7877,35 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>TUMENTA  GRACE</t>
+          <t>KAMDEM MERLIN</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53701</t>
+          <t>SO2604-51411</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -8389,19 +7922,19 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>YFOU JASINO PEGUY</t>
+          <t>ETABLISSEMENT KAFAB SARL (KAMDEM FOTSO ACHILLE BERTRAND)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>SO2604-51904</t>
+          <t>SO2604-53917</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>23000</v>
+        <v>2300</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>23000</v>
+        <v>2300</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -8420,26 +7953,26 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>TEDONGMO ZOYIM AGOSTINI</t>
+          <t>TUMENTA  GRACE</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52115</t>
+          <t>SO2604-53701</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -8458,26 +7991,26 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>SOFAB PROVENDERIE</t>
+          <t>YFOU JASINO PEGUY</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52011</t>
+          <t>SO2604-51904</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>4400</v>
+        <v>23000</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>4400</v>
+        <v>23000</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -8496,35 +8029,35 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>BOUKAR ISAIE</t>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52017</t>
+          <t>SO2604-52115</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>3100</v>
+        <v>8500</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3100</v>
+        <v>8500</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -8541,28 +8074,28 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Bah And Sons Company Ltd</t>
+          <t>SOFAB PROVENDERIE</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53332</t>
+          <t>SO2604-52011</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -8579,28 +8112,28 @@
     <row r="44">
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>PROVENDERIE LA GRACE</t>
+          <t>BOUKAR ISAIE</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52460</t>
+          <t>SO2604-52017</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>9000</v>
+        <v>3100</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>9000</v>
+        <v>3100</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -8610,35 +8143,35 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>MEMGBA MESSI ALBERTINE FLEUR (MEMGBA MESSI ALBERTINE FLEUR)</t>
+          <t>Bah And Sons Company Ltd</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>SO2604-52840</t>
+          <t>SO2604-53332</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5300</v>
+        <v>2000</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5300</v>
+        <v>2000</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -8648,26 +8181,26 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>TOTUE BOREL</t>
+          <t>PROVENDERIE LA GRACE</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53184</t>
+          <t>SO2604-52460</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -8686,35 +8219,35 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>TIEDAM EMMANUEL</t>
+          <t>MEMGBA MESSI ALBERTINE FLEUR (MEMGBA MESSI ALBERTINE FLEUR)</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53250</t>
+          <t>SO2604-52840</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4050</v>
+        <v>5300</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>4050</v>
+        <v>5300</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -8724,26 +8257,26 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Tokam Fotie Jean Jacques</t>
+          <t>TOTUE BOREL</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53253</t>
+          <t>SO2604-53184</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -8769,19 +8302,19 @@
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>TCHUENTE SYLVAIN</t>
+          <t>TIEDAM EMMANUEL</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>SO2604-54105</t>
+          <t>SO2604-53250</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>16000</v>
+        <v>4050</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>16000</v>
+        <v>4050</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -8800,35 +8333,35 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>FOPA MATHIEU MATHURIN</t>
+          <t>Tokam Fotie Jean Jacques</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>SO2604-54153</t>
+          <t>SO2604-53253</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>5500</v>
+        <v>2400</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>5500</v>
+        <v>2400</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -8838,35 +8371,35 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Haman Soudi</t>
+          <t>TCHUENTE SYLVAIN</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53962</t>
+          <t>SO2604-54105</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -8876,35 +8409,35 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>NOUMSSI HERVE</t>
+          <t>FOPA MATHIEU MATHURIN</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>SO2604-53967</t>
+          <t>SO2604-54153</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -8921,28 +8454,28 @@
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>TAMOU JEAN ROBERT</t>
+          <t>Haman Soudi</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55177</t>
+          <t>SO2604-53962</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -8959,28 +8492,28 @@
     <row r="54">
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>TSOPANOUA VICTOR</t>
+          <t>NOUMSSI HERVE</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>SO2605-54853</t>
+          <t>SO2604-53967</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>6200</v>
+        <v>2700</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>6200</v>
+        <v>2700</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -8990,35 +8523,35 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Foumane Andre Desire</t>
+          <t>TAMOU JEAN ROBERT</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>SO2605-54833</t>
+          <t>SO2605-55177</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -9028,35 +8561,35 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>WAFO FOBA ARMAND</t>
+          <t>TSOPANOUA VICTOR</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55580</t>
+          <t>SO2605-54853</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>4000</v>
+        <v>6200</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>4000</v>
+        <v>6200</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -9066,35 +8599,35 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>TOUKAM TAFAM GHISLAIN</t>
+          <t>Foumane Andre Desire</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55706</t>
+          <t>SO2605-54833</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -9104,35 +8637,35 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Ngouana Anselme</t>
+          <t>WAFO FOBA ARMAND</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>SO2605-54348</t>
+          <t>SO2605-55580</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -9142,35 +8675,35 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>MARSHAL  FARMERS</t>
+          <t>TOUKAM TAFAM GHISLAIN</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>SO2605-54941</t>
+          <t>SO2605-55706</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -9180,35 +8713,35 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>NZONTHEU PAUL</t>
+          <t>Ngouana Anselme</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55738</t>
+          <t>SO2605-54348</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -9225,28 +8758,28 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DOM KANSE ERIC JULIEN</t>
+          <t>MARSHAL  FARMERS</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55722</t>
+          <t>SO2605-54941</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -9263,19 +8796,19 @@
     <row r="62">
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>TCHEMBENG ANTOINE</t>
+          <t>NZONTHEU PAUL</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>SO2605-55879</t>
+          <t>SO2605-55738</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>10000</v>
+        <v>5500</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>10000</v>
+        <v>5500</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -9284,7 +8817,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -9294,35 +8827,35 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>BEI KEVINE ACHU</t>
+          <t>DOM KANSE ERIC JULIEN</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56117</t>
+          <t>SO2605-55722</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -9332,35 +8865,35 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Moromte Oscar</t>
+          <t>TCHEMBENG ANTOINE</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56023</t>
+          <t>SO2605-55879</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -9377,28 +8910,28 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>GIC PRADUCAM</t>
+          <t>BEI KEVINE ACHU</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56131</t>
+          <t>SO2605-56117</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -9408,35 +8941,35 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>KOAGNE TCHOUDA DADINE CAROLLE</t>
+          <t>Moromte Oscar</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56200</t>
+          <t>SO2605-56023</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -9446,35 +8979,35 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Sandeep Tirkey</t>
+          <t>GIC PRADUCAM</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56126</t>
+          <t>SO2605-56131</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -9484,35 +9017,35 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>GIC PRADUCAM</t>
+          <t>KOAGNE TCHOUDA DADINE CAROLLE</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56141</t>
+          <t>SO2605-56200</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -9522,35 +9055,35 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>GIC PRADUCAM</t>
+          <t>Sandeep Tirkey</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>SO2605-56146</t>
+          <t>SO2605-56126</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -9560,43 +9093,119 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="5" t="inlineStr">
         <is>
+          <t>GIC PRADUCAM</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-56141</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>GIC PRADUCAM</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>SO2605-56146</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
           <t>TAMEDJO CYRILLE</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>SO2604-54070</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n">
+      <c r="D72" s="5" t="n">
         <v>6150</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E72" s="5" t="n">
         <v>6150</v>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>BELGO-NDJELENG</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>NON ÉCHUE</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
@@ -29128,17 +28737,17 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Même jour que PONTE (10/06/2026)</t>
+          <t>Même jour que PONTE (05/06/2026)</t>
         </is>
       </c>
     </row>
@@ -29183,17 +28792,17 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Même jour que PONTE (11/06/2026)</t>
+          <t>Même jour que PONTE (19/06/2026)</t>
         </is>
       </c>
     </row>
@@ -29308,13 +28917,13 @@
         </is>
       </c>
       <c r="D5" s="23" t="n">
-        <v>30000</v>
+        <v>27800</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>27800</v>
+        <v>26400</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>2200</v>
+        <v>1400</v>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
@@ -29335,13 +28944,13 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>38000</v>
+        <v>35700</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>35700</v>
+        <v>33900</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
@@ -29362,13 +28971,13 @@
         </is>
       </c>
       <c r="D7" s="23" t="n">
-        <v>15000</v>
+        <v>12800</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>12800</v>
+        <v>12150</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>2200</v>
+        <v>650</v>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
@@ -29389,13 +28998,13 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>38000</v>
+        <v>35300</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>35300</v>
+        <v>33550</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>2700</v>
+        <v>1750</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
@@ -29416,13 +29025,13 @@
         </is>
       </c>
       <c r="D9" s="23" t="n">
-        <v>30000</v>
+        <v>27100</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>27100</v>
+        <v>25750</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>2900</v>
+        <v>1350</v>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
@@ -29443,17 +29052,17 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>38000</v>
+        <v>35900</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>35900</v>
+        <v>34100</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Littoral + Nord</t>
+          <t>Centre + Littoral</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr"/>
@@ -29466,13 +29075,13 @@
       </c>
       <c r="C11" s="24" t="inlineStr"/>
       <c r="D11" s="24" t="n">
-        <v>189000</v>
+        <v>174600</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>174600</v>
+        <v>165850</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>14400</v>
+        <v>8750</v>
       </c>
       <c r="G11" s="24" t="inlineStr"/>
       <c r="H11" s="24" t="inlineStr"/>

--- a/Prog poussin/Popo/output/Plan_Livraisons_BELGO_Ponte.xlsx
+++ b/Prog poussin/Popo/output/Plan_Livraisons_BELGO_Ponte.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L77"/>
+  <dimension ref="B2:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -927,7 +927,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ven 05/06/2026 — Production: 35,700 | Region: Centre + Littoral | Place libre: 2,750 [Littoral minime: 5,850 (ÉCHUE: 5,850)]</t>
+          <t>Ven 05/06/2026 — Production: 35,700 | Region: Centre + Littoral | Place libre: 0 [Littoral minime: 5,850 (ÉCHUE: 5,850)]</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -1050,19 +1050,19 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TAMATIO</t>
+          <t>KENMEGNE EPSE KOUAM THERESE SYLVIE</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52536</t>
+          <t>SO2602-46588</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -1071,24 +1071,20 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>BELGO AHALA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
@@ -1101,19 +1097,19 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>DJEMENI KAMENI</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53611</t>
+          <t>SO2603-48511</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4500</v>
+        <v>1700</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>4500</v>
+        <v>1700</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -1122,24 +1118,20 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKOLBISSON</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
@@ -1152,19 +1144,19 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Emale Tache Bertrand Patrick (42E32)</t>
+          <t>Gic Producteurs De Mais De Yaounde (Ebot Wilfred Besong)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53565</t>
+          <t>SO2601-42254</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -1173,24 +1165,20 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO AHALA</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
@@ -1203,19 +1191,19 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55438</t>
+          <t>SO2605-55799</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3200</v>
+        <v>50</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>4250</v>
+        <v>16650</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1229,17 +1217,17 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
+          <t>RECLASSÉE</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
         </is>
       </c>
     </row>
@@ -1254,19 +1242,19 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>TAMATIO</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55438</t>
+          <t>SO2604-52536</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4250</v>
+        <v>1100</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -1275,12 +1263,12 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO AHALA</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1290,7 +1278,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1298,14 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55641</t>
+          <t>SO2604-53611</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1331,7 +1319,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1356,19 +1344,19 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>Emale Tache Bertrand Patrick (42E32)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52423</t>
+          <t>SO2604-53565</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1382,15 +1370,19 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr"/>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
@@ -1403,209 +1395,350 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55438</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>35700</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55438</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>35700</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
           <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-55799</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>3800</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>16650</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55641</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>BELGO-MESSASSI</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>35700</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Cheuko Arsene Kevin</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55832</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Suite -&gt; 10/06 (5j) | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="8" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Suite -&gt; 10/06 (5j) | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Sous-total Ven 05/06</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="8" t="n">
-        <v>32950</v>
-      </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="12" t="n">
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="8" t="n">
+        <v>35700</v>
+      </c>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Mer 10/06/2026 — Production: 12,800 | Region: Centre | Place libre: 150</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-52423</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Cheuko Arsene Kevin</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55832</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>2750</v>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Mer 10/06/2026 — Production: 12,800 | Region: Centre | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>12800</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-55799</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>12800</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>16650</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="G31" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>BELGO-MESSASSI</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Sous-total Mer 10/06</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="8" t="n">
-        <v>12800</v>
-      </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Jeu 11/06/2026 — Production: 35,300 | Region: Ouest | Place libre: 1,050</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>35300</v>
+        <v>12800</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TALLA TAGNE SERGE RICHARD</t>
+          <t>KENNE TAKALA BRICE</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>SO2605-54827</t>
+          <t>SO2605-55818</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -1616,722 +1749,1528 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Sous-total Mer 10/06</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="8" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Qté manquante pour compléter la production</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>Capacité disponible pour insertion ultérieure</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Jeu 11/06/2026 — Production: 35,300 | Region: Ouest | Place libre: 0</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>35300</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TALLA TAGNE SERGE RICHARD</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-54827</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>BELGO-NDJELENG</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
         <is>
           <t>ÉCHUE</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Mouvement systeme (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C38" s="6" t="n">
         <v>35300</v>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Wayap Guy Merlin</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>SO2602-45568</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>5200</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G38" s="6" t="n">
         <v>5200</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>BELGO-FAMLA</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>ÉCHUE</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>Mouvement systeme (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C39" s="6" t="n">
         <v>35300</v>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>TCHINDA KAAWE SOL PLEISIS</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>SO2601-44631</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>17250</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G39" s="6" t="n">
         <v>17250</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>BELGO-FAMLA</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>ÉCHUE RECLASSÉE</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C40" s="6" t="n">
         <v>35300</v>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>TEDONGMO ZOYIM AGOSTINI</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>SO2604-52115</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>8500</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G40" s="6" t="n">
         <v>8500</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>BELGO MBOUDA</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>RECLASSÉE</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>35300</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TENJEI PETER</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57685</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>35300</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>KUATE NOKAM GUY SALOMON</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>SO2602-46922</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Sous-total Jeu 11/06</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="8" t="n">
-        <v>34250</v>
-      </c>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="12" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Lun 15/06/2026 — Production: 27,100 | Region: - | Place libre: 27,100</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Sous-total Lun 15/06</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="12" t="n">
-        <v>27100</v>
-      </c>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="11" t="n"/>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Ven 19/06/2026 — Production: 35,900 | Region: Ouest | Place libre: 15,700</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>35900</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TSOPANOUA VICTOR</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-54853</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>BELGO MBOUDA</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="8" t="n">
+        <v>35300</v>
+      </c>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>35900</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TCHEMBENG ANTOINE</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-55879</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Lun 15/06/2026 — Production: 27,100 | Region: Centre + Littoral | Place libre: 0 [Littoral minime: 3,300 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55799</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>16600</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>16650</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>WANDJI ELISABETH</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-56192</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Cheuko Arsene Kevin</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57248</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Koumetio Keubou David Herve</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55726</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NKONGSAMBA</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>SO2603-49472</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Lukong Epse Ebango</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>SO2606-57981</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>MAGDALENE KUKU EYOH</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57737</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Chefor Shadrack Nchang</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-53200</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-BUEA</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Sous-total Lun 15/06</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="8" t="n">
+        <v>27100</v>
+      </c>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Ven 19/06/2026 — Production: 35,900 | Region: Ouest | Place libre: 0</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C57" s="6" t="n">
         <v>35900</v>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>TSOPANOUA VICTOR</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-54853</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>TCHEMBENG ANTOINE</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55879</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>NGUELLA MARTIN</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>SO2511-36933</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F59" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G59" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>BELGO-FAMLA</t>
         </is>
       </c>
-      <c r="J46" s="6" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>19/09/2026</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>RECLASSÉE</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="8" t="inlineStr">
+      <c r="L59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>NZONTHEU PAUL</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55738</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Bah And Sons Company Ltd</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-53332</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>KUATE NOKAM GUY SALOMON</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>SO2602-46922</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>MAFEUGANG FLORENCE</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57306</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>35900</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>GATCHUESSI</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-56493</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Sous-total Ven 19/06</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="8" t="n">
-        <v>20200</v>
-      </c>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="12" t="n">
-        <v>15700</v>
-      </c>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="11" t="n"/>
-      <c r="K48" s="11" t="n"/>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="13" t="inlineStr">
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="8" t="n">
+        <v>35900</v>
+      </c>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+      <c r="L65" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>TOTAL GENERAL LIVRE</t>
         </is>
       </c>
-      <c r="C50" s="14" t="n"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="13" t="n">
-        <v>128000</v>
-      </c>
-      <c r="G50" s="14" t="n"/>
-      <c r="H50" s="14" t="n"/>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="14" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="15" t="inlineStr">
+      <c r="C67" s="14" t="n"/>
+      <c r="D67" s="14" t="n"/>
+      <c r="E67" s="14" t="n"/>
+      <c r="F67" s="13" t="n">
+        <v>174450</v>
+      </c>
+      <c r="G67" s="14" t="n"/>
+      <c r="H67" s="14" t="n"/>
+      <c r="I67" s="14" t="n"/>
+      <c r="J67" s="14" t="n"/>
+      <c r="K67" s="14" t="n"/>
+      <c r="L67" s="14" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>TOTAL QTE MANQUANTE (capacité disponible)</t>
         </is>
       </c>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="16" t="n">
-        <v>46600</v>
-      </c>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="11" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="11" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>Legende :</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="18" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>ECHUE</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Commande dont la date prevue de livraison est depassee</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="18" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>ECHUE RECLASSEE</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Commande echue + reclassee (date_modif &lt; date_prevue - 5j)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="18" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>IMMINENTE</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr">
         <is>
           <t>Livraison prevue &lt;=10j — integree uniquement en force majeure</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="18" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>NON ECHUE</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Livraison pas encore due — non integrable</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="18" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="18" t="inlineStr">
         <is>
           <t>SPLIT</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
         <is>
           <t>Livraison partielle — premier split &gt;= 50% de la qte totale, pas de 2e split</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="18" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>FORCE MAJEURE</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D76" s="19" t="inlineStr">
         <is>
           <t>Commande imminente integree pour remplir la capacite</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="18" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>EST+NORD</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D77" s="19" t="inlineStr">
         <is>
           <t>Est et Nord toujours programmes le meme jour (preference jeu/ven)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="18" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="18" t="inlineStr">
         <is>
           <t>MOUVEMENT SYSTEME</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>Mouvement automatique Proctor Ai "En cours" (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="18" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="18" t="inlineStr">
         <is>
           <t>QTE MANQUANTE</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Capacite non utilisee — disponible pour insertion ulterieure (pas de split force)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="17" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>Contraintes appliquees :</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="20" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="20" t="inlineStr">
         <is>
           <t>1. FIFO par date de livraison prevue (echues en priorite)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="20" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>2. Commandes &lt;=1000 echues traitees en premier (sauf Est/Nord -&gt; meme jour)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="20" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="20" t="inlineStr">
         <is>
           <t>3. Est et Nord TOUJOURS programmes le meme jour (preference jeu/ven pour eclosion)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="20" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>4. Une region principale par jour (completee si capacite restante)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="20" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="20" t="inlineStr">
         <is>
           <t>5. Client TEDONGMO YEMDJI FRANCK exclu</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="20" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="20" t="inlineStr">
         <is>
           <t>6. Commandes en statut Brouillon exclues</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="20" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="20" t="inlineStr">
         <is>
           <t>7. Proctor Ai 'En cours' = mouvement systeme / Proctor Ai 'Livree' = livraison reelle</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="20" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>8. Commandes non echues integrees uniquement en force majeure</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="20" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="20" t="inlineStr">
         <is>
           <t>9. Livraison en 2 fois possible : 2-3j meme semaine, 4-5j cross-semaine</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="20" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>10. Quantites deja livrees (reelles) deduites via fichier A traiter</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="20" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="20" t="inlineStr">
         <is>
           <t>11. Cross-reference expeditions pour filtrage Proctor Ai + Status Commande</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="20" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="20" t="inlineStr">
         <is>
           <t>12. Date de reference: 09/05/2026 (dates anterieures exclues)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="20" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>13. Pas de split non pertinent: premier split &gt;= 50% de la qte totale, pas de 2e split (totalite du reste) — capacite restante = qte manquante informative</t>
         </is>
@@ -2348,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L77"/>
+  <dimension ref="B2:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2711,7 +3650,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ven 05/06/2026 — Production: 33,900 | Region: Centre + Littoral | Place libre: 900 [Littoral minime: 7,250 (ÉCHUE: 7,250)]</t>
+          <t>Ven 05/06/2026 — Production: 33,900 | Region: Centre + Littoral | Place libre: 0 [Littoral minime: 8,150 (ÉCHUE: 7,250)]</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -2834,19 +3773,19 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TAMATIO</t>
+          <t>KENMEGNE EPSE KOUAM THERESE SYLVIE</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52536</t>
+          <t>SO2602-46588</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -2855,24 +3794,20 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>BELGO AHALA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
@@ -2885,19 +3820,19 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>DJEMENI KAMENI</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53611</t>
+          <t>SO2603-48511</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4500</v>
+        <v>1700</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>4500</v>
+        <v>1700</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -2906,24 +3841,20 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKOLBISSON</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
@@ -2936,19 +3867,19 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Emale Tache Bertrand Patrick (42E32)</t>
+          <t>Gic Producteurs De Mais De Yaounde (Ebot Wilfred Besong)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53565</t>
+          <t>SO2601-42254</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -2957,24 +3888,20 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO AHALA</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
@@ -2987,19 +3914,19 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55438</t>
+          <t>SO2605-55799</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2550</v>
+        <v>2050</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>4250</v>
+        <v>16650</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -3013,12 +3940,12 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE</t>
+          <t>RECLASSÉE</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -3038,19 +3965,19 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>TAMATIO</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55438</t>
+          <t>SO2604-52536</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1700</v>
+        <v>1100</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4250</v>
+        <v>1100</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -3059,12 +3986,12 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO AHALA</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -3074,7 +4001,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
@@ -3094,14 +4021,14 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55641</t>
+          <t>SO2604-53611</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -3115,7 +4042,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -3140,19 +4067,19 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>Emale Tache Bertrand Patrick (42E32)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52423</t>
+          <t>SO2604-53565</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -3166,15 +4093,19 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>ÉCHUE RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr"/>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
@@ -3187,340 +4118,368 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55438</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TAKAMTSING PROSPER</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55438</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>33900</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>WANDJI ELISABETH</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-56192</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-BERI</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Sous-total Ven 05/06</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="8" t="n">
+        <v>33900</v>
+      </c>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Mer 10/06/2026 — Production: 12,150 | Region: Centre | Place libre: 0</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
           <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-55799</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>16650</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55641</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>BELGO-MESSASSI</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-52423</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>12150</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>KENNE TAKALA BRICE</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55818</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Suite -&gt; 10/06 (5j) | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Sous-total Ven 05/06</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="8" t="n">
-        <v>33000</v>
-      </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Mer 10/06/2026 — Production: 12,150 | Region: Centre | Place libre: 0</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Sous-total Mer 10/06</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="8" t="n">
         <v>12150</v>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-55799</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>12150</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>16650</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Sous-total Mer 10/06</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="8" t="n">
-        <v>12150</v>
-      </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Jeu 11/06/2026 — Production: 33,550 | Region: Ouest | Place libre: 0</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>33550</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TALLA TAGNE SERGE RICHARD</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-54827</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>3300</v>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>33550</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Wayap Guy Merlin</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>SO2602-45568</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>ÉCHUE</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Mouvement systeme (pas de livraison reelle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>33550</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TCHINDA KAAWE SOL PLEISIS</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>SO2601-44631</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>17250</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>17250</v>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>ÉCHUE RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
@@ -3533,93 +4492,206 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
+          <t>TALLA TAGNE SERGE RICHARD</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-54827</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Wayap Guy Merlin</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>SO2602-45568</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TCHINDA KAAWE SOL PLEISIS</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>SO2601-44631</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>17250</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>17250</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>ÉCHUE RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>33550</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
           <t>TEDONGMO ZOYIM AGOSTINI</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>SO2604-52115</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>7800</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G38" s="6" t="n">
         <v>8500</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>BELGO MBOUDA</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>RECLASSÉE</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Sous-total Jeu 11/06</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="8" t="n">
-        <v>33550</v>
-      </c>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Lun 15/06/2026 — Production: 25,750 | Region: - | Place libre: 25,750</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Sous-total Lun 15/06</t>
+          <t>Sous-total Jeu 11/06</t>
         </is>
       </c>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="8" t="n">
-        <v>0</v>
+        <v>33550</v>
       </c>
       <c r="G39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
@@ -3628,249 +4700,289 @@
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
     </row>
-    <row r="40">
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="12" t="n">
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Lun 15/06/2026 — Production: 25,750 | Region: Centre + Littoral | Place libre: 0 [Littoral minime: 600 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
         <v>25750</v>
       </c>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="11" t="n"/>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Ven 19/06/2026 — Production: 34,100 | Region: Ouest | Place libre: 13,200</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55799</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>14600</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>16650</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-MESSASSI</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>34100</v>
+        <v>25750</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TEDONGMO ZOYIM AGOSTINI</t>
+          <t>Cheuko Arsene Kevin</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52115</t>
+          <t>SO2605-55832</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>700</v>
+        <v>6000</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>8500</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
+          <t>IMMINENTE</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>34100</v>
+        <v>25750</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TSOPANOUA VICTOR</t>
+          <t>KENNE TAKALA BRICE</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>SO2605-54853</t>
+          <t>SO2605-55818</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>6200</v>
+        <v>600</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>6200</v>
+        <v>3300</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr"/>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>34100</v>
+        <v>25750</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TCHEMBENG ANTOINE</t>
+          <t>WANDJI ELISABETH</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55879</t>
+          <t>SO2605-56192</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr"/>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>34100</v>
+        <v>25750</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>NGUELLA MARTIN</t>
+          <t>Cheuko Arsene Kevin</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>SO2511-36933</t>
+          <t>SO2605-57248</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr"/>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure) | FORCE MAJEURE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Sous-total Ven 19/06</t>
+          <t>Sous-total Lun 15/06</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="8" t="n">
-        <v>20900</v>
+        <v>25750</v>
       </c>
       <c r="G47" s="9" t="n"/>
       <c r="H47" s="9" t="n"/>
@@ -3879,275 +4991,818 @@
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
     </row>
-    <row r="48">
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Qté manquante pour compléter la production</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="12" t="n">
-        <v>13200</v>
-      </c>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="11" t="n"/>
-      <c r="K48" s="11" t="n"/>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>Capacité disponible pour insertion ultérieure</t>
-        </is>
-      </c>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Ven 19/06/2026 — Production: 34,100 | Region: Littoral + Ouest | Place libre: 0 [Littoral minime: 200 (ÉCHUE: 0)]</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-52115</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | LIVRAISON PARTIELLE | Partiel (solde -&gt; production ulterieure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TSOPANOUA VICTOR</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-54853</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TCHEMBENG ANTOINE</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55879</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>NGUELLA MARTIN</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>SO2511-36933</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>RECLASSÉE</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TENJEI PETER</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57685</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>NZONTHEU PAUL</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55738</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Bah And Sons Company Ltd</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>SO2604-53332</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Mouvement systeme (pas de livraison reelle) | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>KUATE NOKAM GUY SALOMON</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>SO2602-46922</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-FAMLA</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>MAFEUGANG FLORENCE</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-57306</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>BELGO MBOUDA</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Koumetio Keubou David Herve</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55726</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NKONGSAMBA</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Fokou Nono Herve Raoul</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>SO2605-55346</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>BELGO-NDJELENG</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>NON ÉCHUE</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=1000 | FORCE MAJEURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Sous-total Ven 19/06</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="8" t="n">
+        <v>34100</v>
+      </c>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>TOTAL GENERAL LIVRE</t>
         </is>
       </c>
-      <c r="C50" s="14" t="n"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="13" t="n">
-        <v>126000</v>
-      </c>
-      <c r="G50" s="14" t="n"/>
-      <c r="H50" s="14" t="n"/>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="14" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL QTE MANQUANTE (capacité disponible)</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="16" t="n">
-        <v>39850</v>
-      </c>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="C63" s="14" t="n"/>
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="13" t="n">
+        <v>165850</v>
+      </c>
+      <c r="G63" s="14" t="n"/>
+      <c r="H63" s="14" t="n"/>
+      <c r="I63" s="14" t="n"/>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="14" t="n"/>
+      <c r="L63" s="14" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Legende :</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="18" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>ECHUE</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Commande dont la date prevue de livraison est depassee</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="18" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>ECHUE RECLASSEE</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Commande echue + reclassee (date_modif &lt; date_prevue - 5j)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="18" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>IMMINENTE</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Livraison prevue &lt;=10j — integree uniquement en force majeure</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="18" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>NON ECHUE</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Livraison pas encore due — non integrable</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="18" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>SPLIT</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Livraison partielle — premier split &gt;= 50% de la qte totale, pas de 2e split</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="18" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>FORCE MAJEURE</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Commande imminente integree pour remplir la capacite</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="18" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>EST+NORD</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Est et Nord toujours programmes le meme jour (preference jeu/ven)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="18" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>MOUVEMENT SYSTEME</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr">
         <is>
           <t>Mouvement automatique Proctor Ai "En cours" (pas de livraison reelle)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="18" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>QTE MANQUANTE</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Capacite non utilisee — disponible pour insertion ulterieure (pas de split force)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="17" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>Contraintes appliquees :</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="20" t="inlineStr">
-        <is>
-          <t>1. FIFO par date de livraison prevue (echues en priorite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="20" t="inlineStr">
-        <is>
-          <t>2. Commandes &lt;=1000 echues traitees en premier (sauf Est/Nord -&gt; meme jour)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>3. Est et Nord TOUJOURS programmes le meme jour (preference jeu/ven pour eclosion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="20" t="inlineStr">
-        <is>
-          <t>4. Une region principale par jour (completee si capacite restante)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>5. Client TEDONGMO YEMDJI FRANCK exclu</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="20" t="inlineStr">
-        <is>
-          <t>6. Commandes en statut Brouillon exclues</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>7. Proctor Ai 'En cours' = mouvement systeme / Proctor Ai 'Livree' = livraison reelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="20" t="inlineStr">
-        <is>
-          <t>8. Commandes non echues integrees uniquement en force majeure</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="20" t="inlineStr">
-        <is>
-          <t>9. Livraison en 2 fois possible : 2-3j meme semaine, 4-5j cross-semaine</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="20" t="inlineStr">
-        <is>
-          <t>10. Quantites deja livrees (reelles) deduites via fichier A traiter</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>11. Cross-reference expeditions pour filtrage Proctor Ai + Status Commande</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="20" t="inlineStr">
-        <is>
-          <t>12. Date de reference: 09/05/2026 (dates anterieures exclues)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>1. FIFO par date de livraison prevue (echues en priorite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>2. Commandes &lt;=1000 echues traitees en premier (sauf Est/Nord -&gt; meme jour)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>3. Est et Nord TOUJOURS programmes le meme jour (preference jeu/ven pour eclosion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>4. Une region principale par jour (completee si capacite restante)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>5. Client TEDONGMO YEMDJI FRANCK exclu</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>6. Commandes en statut Brouillon exclues</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>7. Proctor Ai 'En cours' = mouvement systeme / Proctor Ai 'Livree' = livraison reelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>8. Commandes non echues integrees uniquement en force majeure</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>9. Livraison en 2 fois possible : 2-3j meme semaine, 4-5j cross-semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>10. Quantites deja livrees (reelles) deduites via fichier A traiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>11. Cross-reference expeditions pour filtrage Proctor Ai + Status Commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>12. Date de reference: 09/05/2026 (dates anterieures exclues)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>13. Pas de split non pertinent: premier split &gt;= 50% de la qte totale, pas de 2e split (totalite du reste) — capacite restante = qte manquante informative</t>
         </is>
@@ -4164,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I108"/>
+  <dimension ref="B2:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4230,19 +5885,19 @@
     <row r="5">
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>Cheuko Arsene Kevin</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55799</t>
+          <t>SO2605-57248</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>2050</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>16650</v>
+        <v>6000</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -4256,221 +5911,221 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
+          <t>IMMINENTE</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>KENMEGNE EPSE KOUAM THERESE SYLVIE</t>
+          <t>GATCHUESSI</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>SO2602-46588</t>
+          <t>SO2605-56493</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1150</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1150</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
+          <t>IMMINENTE</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>DJEMENI KAMENI</t>
+          <t>KAMLA DIMITRE</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>SO2603-48511</t>
+          <t>SO2605-57403</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOLBISSON</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
+          <t>IMMINENTE</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Gic Producteurs De Mais De Yaounde (Ebot Wilfred Besong)</t>
+          <t>TIWA</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>SO2601-42254</t>
+          <t>SO2605-57556</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>BELGO AHALA</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>RECLASSÉE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TENJEI PETER</t>
+          <t>LAMINE BOUBA</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57685</t>
+          <t>SO2606-58005</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>500</v>
+        <v>2200</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>500</v>
+        <v>2200</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>NZONTHEU PAUL</t>
+          <t>LAMINE BOUBA</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55738</t>
+          <t>SO2606-58000</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5500</v>
+        <v>1050</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5500</v>
+        <v>1050</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Bah And Sons Company Ltd</t>
+          <t>KOAGNE ALAIN</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53332</t>
+          <t>SO2605-57754</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2000</v>
+        <v>4200</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2000</v>
+        <v>4200</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -4479,340 +6134,340 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Cheuko Arsene Kevin</t>
+          <t>PEKA TAGNE IGNACE</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55832</t>
+          <t>SO2602-47700</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6000</v>
+        <v>9250</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6000</v>
+        <v>9250</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>KENNE TAKALA BRICE</t>
+          <t>HAMIDOU MOUSSA</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55818</t>
+          <t>SO2605-57151</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3300</v>
+        <v>1300</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3300</v>
+        <v>1300</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>WANDJI ELISABETH</t>
+          <t>DOUANLA SIMPLICE</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56192</t>
+          <t>SO2603-48403</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Cheuko Arsene Kevin</t>
+          <t>PEKA TAGNE IGNACE</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57248</t>
+          <t>SO2605-55242</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6000</v>
+        <v>12750</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6000</v>
+        <v>12750</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>KUATE NOKAM GUY SALOMON</t>
+          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>SO2602-46922</t>
+          <t>SO2605-55433</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1100</v>
+        <v>8850</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1100</v>
+        <v>8850</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>MAFEUGANG FLORENCE</t>
+          <t>TAMGOU KADJE DANIEL FRANCK</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57306</t>
+          <t>SO2605-57780</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>GATCHUESSI</t>
+          <t>SOFAB PROVENDERIE</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56493</t>
+          <t>SO2603-49185</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>KAMLA DIMITRE</t>
+          <t>GLOBAL BUSINESS</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57403</t>
+          <t>SO2603-48726</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2100</v>
+        <v>23500</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>2100</v>
+        <v>23500</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>IMMINENTE</t>
+          <t>NON ÉCHUE</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TIWA</t>
+          <t>Kenne Manfouo Idrice</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57556</t>
+          <t>SO2605-57744</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1400</v>
+        <v>16000</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1400</v>
+        <v>16000</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
@@ -4821,7 +6476,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -4831,35 +6486,35 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>LAMINE BOUBA</t>
+          <t>TAKAMTSING PROSPER</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>SO2606-58005</t>
+          <t>SO2603-49472</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2200</v>
+        <v>200</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2200</v>
+        <v>200</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -4869,35 +6524,35 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>LAMINE BOUBA</t>
+          <t>ETS FERME NGASCHO (4E94)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>SO2606-58000</t>
+          <t>SO2603-49488</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1050</v>
+        <v>4700</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1050</v>
+        <v>4700</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -4907,35 +6562,35 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>KOAGNE ALAIN</t>
+          <t>Lukong Epse Ebango</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57754</t>
+          <t>SO2606-57981</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -4945,35 +6600,35 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>PEKA TAGNE IGNACE</t>
+          <t>WAFIN GAELLE</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>SO2602-47700</t>
+          <t>SO2603-49436</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>9250</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>9250</v>
+        <v>10000</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -4983,35 +6638,35 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Koumetio Keubou David Herve</t>
+          <t>GIC FAMES</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55726</t>
+          <t>SO2603-49511</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>200</v>
+        <v>4200</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>200</v>
+        <v>4200</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKONGSAMBA</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -5021,35 +6676,35 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>HAMIDOU MOUSSA</t>
+          <t>KAMGANG GHISLAIN</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57151</t>
+          <t>SO2603-49742</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1300</v>
+        <v>6500</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1300</v>
+        <v>6500</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -5059,35 +6714,35 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Fokou Nono Herve Raoul</t>
+          <t>Nyonse Tchounkeu Moise</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55346</t>
+          <t>SO2605-57638</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>400</v>
+        <v>6100</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>400</v>
+        <v>6100</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Est</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO BERTOUA</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -5097,26 +6752,26 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>DOUANLA SIMPLICE</t>
+          <t>VOKENG KENANG GUILIANO HERVE</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>SO2603-48403</t>
+          <t>SO2603-49819</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
@@ -5125,7 +6780,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -5135,35 +6790,35 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>PEKA TAGNE IGNACE</t>
+          <t>LAMINE BOUBA</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55242</t>
+          <t>SO2603-50019</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>12750</v>
+        <v>5500</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>12750</v>
+        <v>5500</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -5173,35 +6828,35 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Groupe D'initiative Commune Des Jeunes Producteurs Agropastoraux De L'est (Gic/Jepro-Agro)</t>
+          <t>HAMIDOU MOUSSA</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55433</t>
+          <t>SO2605-57161</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>8850</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>8850</v>
+        <v>1000</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -5211,35 +6866,35 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TAMGOU KADJE DANIEL FRANCK</t>
+          <t>NGOKO DJIMGANG NATHALIE</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57780</t>
+          <t>SO2605-57259</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -5249,35 +6904,35 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>SOFAB PROVENDERIE</t>
+          <t>MIBE GUY MARCIAL</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49185</t>
+          <t>SO2603-50464</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO VILLAGE</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -5287,35 +6942,35 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL BUSINESS</t>
+          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>SO2603-48726</t>
+          <t>SO2604-53508</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -5325,35 +6980,35 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Kenne Manfouo Idrice</t>
+          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57744</t>
+          <t>SO2604-53824</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>16000</v>
+        <v>1500</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>16000</v>
+        <v>1500</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -5363,35 +7018,35 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>TEDONGMO ZOYIM AGOSTINI</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49472</t>
+          <t>SO2605-56807</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -5401,35 +7056,35 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>ETS FERME NGASCHO (4E94)</t>
+          <t>KENNY PATRICK</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49488</t>
+          <t>SO2603-50649</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -5439,26 +7094,26 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Lukong Epse Ebango</t>
+          <t>PROVENDERIE L' ASSURANCE</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>SO2606-57981</t>
+          <t>SO2603-50691</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
@@ -5477,35 +7132,35 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>WAFIN GAELLE</t>
+          <t>NOUPING</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49436</t>
+          <t>SO2604-52451</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -5515,35 +7170,35 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>GIC FAMES</t>
+          <t>TEFACK DASSI HERVE</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49511</t>
+          <t>SO2603-50650</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -5553,35 +7208,35 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>KAMGANG GHISLAIN</t>
+          <t>TAKAMTSING PROSPER</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49742</t>
+          <t>SO2604-51282</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>6500</v>
+        <v>5800</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>6500</v>
+        <v>5800</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -5591,35 +7246,35 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Nyonse Tchounkeu Moise</t>
+          <t>SANDJONG ELIE</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57638</t>
+          <t>SO2604-51281</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>6100</v>
+        <v>2200</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>6100</v>
+        <v>2200</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Est</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>BELGO BERTOUA</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -5629,35 +7284,35 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>VOKENG KENANG GUILIANO HERVE</t>
+          <t>Chefor Shadrack Nchang</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>SO2603-49819</t>
+          <t>SO2604-53200</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>11000</v>
+        <v>1050</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>11000</v>
+        <v>1050</v>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-BUEA</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -5667,35 +7322,35 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>LAMINE BOUBA</t>
+          <t>HASSAN HAROUNA</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>SO2603-50019</t>
+          <t>SO2604-52671</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -5705,35 +7360,35 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>HAMIDOU MOUSSA</t>
+          <t>KENNE TCHUENTE JILDAS ANICET</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57161</t>
+          <t>SO2604-51270</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -5743,35 +7398,35 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>NGOKO DJIMGANG NATHALIE</t>
+          <t>Menquele Rodrigue</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57259</t>
+          <t>SO2604-53285</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>6000</v>
+        <v>1100</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>6000</v>
+        <v>1100</v>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -5781,26 +7436,26 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>MIBE GUY MARCIAL</t>
+          <t>Gic Emocolit Kouakam Vancelas Blaise</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>SO2603-50464</t>
+          <t>SO2605-57502</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
@@ -5819,35 +7474,35 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
+          <t>KAMTA SIEWE EPSE TCHATCHOUA EMILIENNE</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53508</t>
+          <t>SO2604-51800</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2000</v>
+        <v>5200</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>2000</v>
+        <v>5200</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -5857,35 +7512,35 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>ABDOUL NASSER HAMADOU (ABDOUL NASSER HAMADOU)</t>
+          <t>PIEBJOU MICHEL</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53824</t>
+          <t>SO2604-51756</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NKOABANG</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -5895,19 +7550,19 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>TEDONGMO ZOYIM AGOSTINI</t>
+          <t>ABDOUL AZIZ</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56807</t>
+          <t>SO2604-52437</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
@@ -5918,12 +7573,12 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -5933,35 +7588,35 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>KENNY PATRICK</t>
+          <t>KAMDEM MERLIN</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>SO2603-50649</t>
+          <t>SO2604-51411</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3500</v>
+        <v>23000</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>3500</v>
+        <v>23000</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>BELGO-FAMLA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -5971,35 +7626,35 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>PROVENDERIE L' ASSURANCE</t>
+          <t>Ngouadjeu Paul</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>SO2603-50691</t>
+          <t>SO2605-56216</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NKONGSAMBA</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -6009,35 +7664,35 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>NOUPING</t>
+          <t>ETABLISSEMENT KAFAB SARL (KAMDEM FOTSO ACHILLE BERTRAND)</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52451</t>
+          <t>SO2604-53917</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -6047,35 +7702,35 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>TEFACK DASSI HERVE</t>
+          <t>TUMENTA  GRACE</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>SO2603-50650</t>
+          <t>SO2604-53701</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO MBOUDA</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -6085,26 +7740,26 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>TAKAMTSING PROSPER</t>
+          <t>YFOU JASINO PEGUY</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51282</t>
+          <t>SO2604-51904</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>5800</v>
+        <v>23000</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>5800</v>
+        <v>23000</v>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
@@ -6113,7 +7768,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -6123,26 +7778,26 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>SANDJONG ELIE</t>
+          <t>SOFAB PROVENDERIE</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51281</t>
+          <t>SO2604-52011</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2200</v>
+        <v>4400</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2200</v>
+        <v>4400</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
@@ -6151,7 +7806,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -6161,26 +7816,26 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Chefor Shadrack Nchang</t>
+          <t>BOUKAR ISAIE</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53200</t>
+          <t>SO2604-52017</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1050</v>
+        <v>3100</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1050</v>
+        <v>3100</v>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
@@ -6189,7 +7844,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>BELGO-BUEA</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -6199,35 +7854,35 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>HASSAN HAROUNA</t>
+          <t>PROVENDERIE LA GRACE</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52671</t>
+          <t>SO2604-52460</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2200</v>
+        <v>9000</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>2200</v>
+        <v>9000</v>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -6237,26 +7892,26 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>KENNE TCHUENTE JILDAS ANICET</t>
+          <t>MEMGBA MESSI ALBERTINE FLEUR (MEMGBA MESSI ALBERTINE FLEUR)</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51270</t>
+          <t>SO2604-52840</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>3000</v>
+        <v>5300</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3000</v>
+        <v>5300</v>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
@@ -6275,35 +7930,35 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Menquele Rodrigue</t>
+          <t>MAGDALENE KUKU EYOH</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53285</t>
+          <t>SO2605-57737</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-BERI</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -6313,35 +7968,35 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Gic Emocolit Kouakam Vancelas Blaise</t>
+          <t>TOTUE BOREL</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57502</t>
+          <t>SO2604-53184</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>BELGO VILLAGE</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -6351,35 +8006,35 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>KAMTA SIEWE EPSE TCHATCHOUA EMILIENNE</t>
+          <t>TIEDAM EMMANUEL</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51800</t>
+          <t>SO2604-53250</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>5200</v>
+        <v>4050</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>5200</v>
+        <v>4050</v>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -6389,35 +8044,35 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>PIEBJOU MICHEL</t>
+          <t>Tokam Fotie Jean Jacques</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51756</t>
+          <t>SO2604-53253</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKOABANG</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -6427,35 +8082,35 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>ABDOUL AZIZ</t>
+          <t>DJOUWE GUTCHOU JULIETTE STEPHANIE</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52437</t>
+          <t>SO2605-57753</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1000</v>
+        <v>4800</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1000</v>
+        <v>4800</v>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -6465,35 +8120,35 @@
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>KAMDEM MERLIN</t>
+          <t>TCHUENTE SYLVAIN</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51411</t>
+          <t>SO2604-54105</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>23000</v>
+        <v>16000</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>23000</v>
+        <v>16000</v>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -6503,35 +8158,35 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Ngouadjeu Paul</t>
+          <t>FOPA MATHIEU MATHURIN</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56216</t>
+          <t>SO2604-54153</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NKONGSAMBA</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -6541,35 +8196,35 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>ETABLISSEMENT KAFAB SARL (KAMDEM FOTSO ACHILLE BERTRAND)</t>
+          <t>Haman Soudi</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53917</t>
+          <t>SO2604-53962</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -6579,35 +8234,35 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>TUMENTA  GRACE</t>
+          <t>NOUMSSI HERVE</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53701</t>
+          <t>SO2604-53967</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>BELGO MBOUDA</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -6617,35 +8272,35 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>YFOU JASINO PEGUY</t>
+          <t>TAMOU JEAN ROBERT</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>SO2604-51904</t>
+          <t>SO2605-55177</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -6655,26 +8310,26 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>SOFAB PROVENDERIE</t>
+          <t>Foumane Andre Desire</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52011</t>
+          <t>SO2605-54833</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4400</v>
+        <v>5000</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>4400</v>
+        <v>5000</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
@@ -6693,35 +8348,35 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>BOUKAR ISAIE</t>
+          <t>WAFO FOBA ARMAND</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52017</t>
+          <t>SO2605-55580</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3100</v>
+        <v>4000</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>3100</v>
+        <v>4000</v>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -6731,26 +8386,26 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>PROVENDERIE LA GRACE</t>
+          <t>TOUKAM TAFAM GHISLAIN</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52460</t>
+          <t>SO2605-55706</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
@@ -6769,35 +8424,35 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>MEMGBA MESSI ALBERTINE FLEUR (MEMGBA MESSI ALBERTINE FLEUR)</t>
+          <t>Ngouana Anselme</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>SO2604-52840</t>
+          <t>SO2605-54348</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>5300</v>
+        <v>3000</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5300</v>
+        <v>3000</v>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -6807,26 +8462,26 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>MAGDALENE KUKU EYOH</t>
+          <t>MARSHAL  FARMERS</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57737</t>
+          <t>SO2605-54941</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
@@ -6845,35 +8500,35 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TOTUE BOREL</t>
+          <t>DOM KANSE ERIC JULIEN</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53184</t>
+          <t>SO2605-55722</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -6883,26 +8538,26 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>TIEDAM EMMANUEL</t>
+          <t>BEI KEVINE ACHU</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53250</t>
+          <t>SO2606-57982</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4050</v>
+        <v>300</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>4050</v>
+        <v>300</v>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
@@ -6921,26 +8576,26 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Tokam Fotie Jean Jacques</t>
+          <t>BEI KEVINE ACHU</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53253</t>
+          <t>SO2605-56117</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>2400</v>
+        <v>10000</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>2400</v>
+        <v>10000</v>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
@@ -6959,35 +8614,35 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>DJOUWE GUTCHOU JULIETTE STEPHANIE</t>
+          <t>Moromte Oscar</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>SO2605-57753</t>
+          <t>SO2605-56023</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -6997,26 +8652,26 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TCHUENTE SYLVAIN</t>
+          <t>MAKOULO FOKA SIDONIE</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>SO2604-54105</t>
+          <t>SO2605-56506</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
@@ -7025,7 +8680,7 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -7035,26 +8690,26 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>FOPA MATHIEU MATHURIN</t>
+          <t>GIC PRADUCAM</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>SO2604-54153</t>
+          <t>SO2605-56131</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
@@ -7073,35 +8728,35 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Haman Soudi</t>
+          <t>KOAGNE TCHOUDA DADINE CAROLLE</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53962</t>
+          <t>SO2605-56200</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -7111,35 +8766,35 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>NOUMSSI HERVE</t>
+          <t>KAMDEM WAGFIN MERLIN DOUGLAS</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>SO2604-53967</t>
+          <t>SO2605-56568</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>2700</v>
+        <v>1050</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>2700</v>
+        <v>1050</v>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -7149,35 +8804,35 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TAMOU JEAN ROBERT</t>
+          <t>Sandeep Tirkey</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55177</t>
+          <t>SO2605-56126</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -7187,35 +8842,35 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Foumane Andre Desire</t>
+          <t>MERCI NOUDJINGAR</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>SO2605-54833</t>
+          <t>SO2605-56535</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDERE</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -7225,26 +8880,26 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>WAFO FOBA ARMAND</t>
+          <t>GIC PRADUCAM</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55580</t>
+          <t>SO2605-56141</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
@@ -7263,35 +8918,35 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>TOUKAM TAFAM GHISLAIN</t>
+          <t>GIC PRADUCAM</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55706</t>
+          <t>SO2605-56146</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-MESSASSI</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -7301,35 +8956,35 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Ngouana Anselme</t>
+          <t>TALLA ALAIN CLOVIS</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>SO2605-54348</t>
+          <t>SO2605-56536</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDERE</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -7339,35 +8994,35 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>MARSHAL  FARMERS</t>
+          <t>NOUTCHOGOUI TASSE HUBERT</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>SO2605-54941</t>
+          <t>SO2605-56363</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>BELGO-BERI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -7377,26 +9032,26 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>DOM KANSE ERIC JULIEN</t>
+          <t>TAWOTCHUEN KAMGAING ACHIL (TAWOTCHUEN KAMGAING ACHIL)</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>SO2605-55722</t>
+          <t>SO2605-56607</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
@@ -7415,26 +9070,26 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>BEI KEVINE ACHU</t>
+          <t>NOUTCHOGOUI TASSE HUBERT</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>SO2606-57982</t>
+          <t>SO2605-56364</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>300</v>
+        <v>30000</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>300</v>
+        <v>30000</v>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
@@ -7453,26 +9108,26 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>BEI KEVINE ACHU</t>
+          <t>DEBOUA ANATOLE</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56117</t>
+          <t>SO2605-56485</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>10000</v>
+        <v>16700</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>10000</v>
+        <v>16700</v>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
@@ -7481,7 +9136,7 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO-FAMLA</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -7491,35 +9146,35 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Moromte Oscar</t>
+          <t>TAMEDJO CYRILLE</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56023</t>
+          <t>SO2604-54070</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>3000</v>
+        <v>6150</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>3000</v>
+        <v>6150</v>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -7529,26 +9184,26 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>MAKOULO FOKA SIDONIE</t>
+          <t>TCHUINTE BLAISE</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56506</t>
+          <t>SO2605-57391</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
@@ -7567,35 +9222,35 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>GIC PRADUCAM</t>
+          <t>Kenne Manfouo Idrice</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56131</t>
+          <t>SO2605-56687</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>16000</v>
+        <v>34600</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>16000</v>
+        <v>34600</v>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>BELGO-MESSASSI</t>
+          <t>BELGO-NDJELENG</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -7605,35 +9260,35 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>KOAGNE TCHOUDA DADINE CAROLLE</t>
+          <t>TSAFACK  ROBERT</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>SO2605-56200</t>
+          <t>SO2605-57460</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>BELGO-NDJELENG</t>
+          <t>BELGO AHALA</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -7642,538 +9297,6 @@
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>KAMDEM WAGFIN MERLIN DOUGLAS</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56568</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E95" s="6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Sandeep Tirkey</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56126</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E96" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>MERCI NOUDJINGAR</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56535</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E97" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDERE</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>GIC PRADUCAM</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56141</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E98" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>GIC PRADUCAM</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56146</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E99" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>16/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>TALLA ALAIN CLOVIS</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56536</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>11000</v>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>16/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>NOUTCHOGOUI TASSE HUBERT</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56363</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E101" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>TAWOTCHUEN KAMGAING ACHIL (TAWOTCHUEN KAMGAING ACHIL)</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56607</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E102" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-MESSASSI</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>NOUTCHOGOUI TASSE HUBERT</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56364</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E103" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>24/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>DEBOUA ANATOLE</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56485</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="n">
-        <v>16700</v>
-      </c>
-      <c r="E104" s="6" t="n">
-        <v>16700</v>
-      </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>TAMEDJO CYRILLE</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>SO2604-54070</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="n">
-        <v>6150</v>
-      </c>
-      <c r="E105" s="6" t="n">
-        <v>6150</v>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="H105" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>TCHUINTE BLAISE</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-57391</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E106" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-FAMLA</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>30/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>Kenne Manfouo Idrice</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-56687</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="n">
-        <v>34600</v>
-      </c>
-      <c r="E107" s="6" t="n">
-        <v>34600</v>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>BELGO-NDJELENG</t>
-        </is>
-      </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>TSAFACK  ROBERT</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>SO2605-57460</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E108" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>BELGO AHALA</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>NON ÉCHUE</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>07/11/2026</t>
         </is>
@@ -42283,17 +43406,17 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Non planifiée</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>En attente PONTE</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Même jour que PONTE (non planifiée)</t>
+          <t>Même jour que PONTE (10/06/2026)</t>
         </is>
       </c>
     </row>
@@ -42338,17 +43461,17 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Non planifiée</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>En attente PONTE</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>Même jour que PONTE (non planifiée)</t>
+          <t>Même jour que PONTE (19/06/2026)</t>
         </is>
       </c>
     </row>
@@ -42856,7 +43979,7 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Centre + Littoral</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr"/>
